--- a/framework/data/excel/register_hybrid.xlsx
+++ b/framework/data/excel/register_hybrid.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24931"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\_DA\DA4\framework\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F4CF2DF-248E-4008-BBB7-2BB8AE3531C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5783EF-5052-4C26-925A-02E78DADF129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1380" yWindow="3105" windowWidth="12450" windowHeight="13185" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test_step" sheetId="1" r:id="rId1"/>
-    <sheet name="test_case" sheetId="2" r:id="rId2"/>
+    <sheet name="test_cases" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -770,9 +770,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F35"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.33203125" customWidth="1"/>
+    <col min="1" max="1" width="42.28515625" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="19" customWidth="1"/>
     <col min="4" max="4" width="33" customWidth="1"/>
@@ -780,7 +780,7 @@
     <col min="6" max="6" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -800,7 +800,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -816,7 +816,7 @@
       </c>
       <c r="F2" s="2"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>6</v>
       </c>
@@ -834,7 +834,7 @@
       </c>
       <c r="F3" s="3"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -852,7 +852,7 @@
       </c>
       <c r="F4" s="2"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>6</v>
       </c>
@@ -870,7 +870,7 @@
       </c>
       <c r="F5" s="3"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>6</v>
       </c>
@@ -888,7 +888,7 @@
       </c>
       <c r="F6" s="2"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -904,7 +904,7 @@
       <c r="E7" s="3"/>
       <c r="F7" s="3"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
@@ -920,7 +920,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="2"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>6</v>
       </c>
@@ -938,7 +938,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>6</v>
       </c>
@@ -954,7 +954,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>26</v>
       </c>
@@ -970,7 +970,7 @@
       </c>
       <c r="F11" s="3"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>26</v>
       </c>
@@ -988,7 +988,7 @@
       </c>
       <c r="F12" s="2"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="F13" s="3"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>26</v>
       </c>
@@ -1024,7 +1024,7 @@
       </c>
       <c r="F14" s="2"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>26</v>
       </c>
@@ -1042,7 +1042,7 @@
       </c>
       <c r="F15" s="3"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>26</v>
       </c>
@@ -1058,7 +1058,7 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>26</v>
       </c>
@@ -1074,7 +1074,7 @@
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>26</v>
       </c>
@@ -1092,7 +1092,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>28</v>
       </c>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="F19" s="3"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>28</v>
       </c>
@@ -1124,7 +1124,7 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>28</v>
       </c>
@@ -1142,7 +1142,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>28</v>
       </c>
@@ -1160,7 +1160,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>28</v>
       </c>
@@ -1178,7 +1178,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>28</v>
       </c>
@@ -1196,7 +1196,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
@@ -1212,7 +1212,7 @@
       </c>
       <c r="F25" s="3"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>37</v>
       </c>
@@ -1230,7 +1230,7 @@
       </c>
       <c r="F26" s="2"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="F27" s="3"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>37</v>
       </c>
@@ -1266,7 +1266,7 @@
       </c>
       <c r="F28" s="2"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>37</v>
       </c>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>37</v>
       </c>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="F30" s="2"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>37</v>
       </c>
@@ -1318,7 +1318,7 @@
       <c r="E31" s="3"/>
       <c r="F31" s="3"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>37</v>
       </c>
@@ -1336,7 +1336,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>42</v>
       </c>
@@ -1352,7 +1352,7 @@
       </c>
       <c r="F33" s="3"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>42</v>
       </c>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="F34" s="2"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
         <v>42</v>
       </c>
@@ -1398,9 +1398,9 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:Q12"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.88671875" customWidth="1"/>
+    <col min="1" max="1" width="20.85546875" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="3" width="45" customWidth="1"/>
     <col min="4" max="4" width="24" customWidth="1"/>
@@ -1419,7 +1419,7 @@
     <col min="17" max="17" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>46</v>
       </c>
@@ -1472,7 +1472,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>62</v>
       </c>
@@ -1507,7 +1507,7 @@
       <c r="P2" s="2"/>
       <c r="Q2" s="2"/>
     </row>
-    <row r="3" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>72</v>
       </c>
@@ -1544,7 +1544,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>81</v>
       </c>
@@ -1579,7 +1579,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>84</v>
       </c>
@@ -1614,7 +1614,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" ht="25.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>89</v>
       </c>
@@ -1647,7 +1647,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>94</v>
       </c>
@@ -1684,7 +1684,7 @@
       <c r="P7" s="3"/>
       <c r="Q7" s="3"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>99</v>
       </c>
@@ -1721,7 +1721,7 @@
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>105</v>
       </c>
@@ -1758,7 +1758,7 @@
       <c r="P9" s="3"/>
       <c r="Q9" s="3"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>111</v>
       </c>
@@ -1795,7 +1795,7 @@
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
     </row>
-    <row r="11" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>68</v>
       </c>
@@ -1834,7 +1834,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:17" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>77</v>
       </c>

--- a/framework/data/excel/register_hybrid.xlsx
+++ b/framework/data/excel/register_hybrid.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\_DA\DA4\framework\data\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5783EF-5052-4C26-925A-02E78DADF129}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA601458-8526-4272-BEEC-530159701836}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1380" yWindow="3105" windowWidth="12450" windowHeight="13185" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="28320" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="test_step" sheetId="1" r:id="rId1"/>
+    <sheet name="test_steps" sheetId="1" r:id="rId1"/>
     <sheet name="test_cases" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
